--- a/reports/safe_students.xlsx
+++ b/reports/safe_students.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,20 +439,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>PERFORMANCE SCORE</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>REASON</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SUGGESTION</t>
         </is>
@@ -473,20 +478,25 @@
       <c r="D2" t="n">
         <v>65</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>gayee0131@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>71.5</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Good Performance</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Keep up the good work.</t>
         </is>

--- a/reports/safe_students.xlsx
+++ b/reports/safe_students.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,25 +439,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>EMAIL</t>
+          <t>PERFORMANCE SCORE</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>PERFORMANCE SCORE</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>RISK</t>
+          <t>REASON</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>REASON</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>SUGGESTION</t>
         </is>
@@ -465,38 +460,543 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abdul</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D2" t="n">
+        <v>73</v>
+      </c>
+      <c r="E2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>105</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>84</v>
+      </c>
+      <c r="D3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E3" t="n">
+        <v>73</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ram</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>81</v>
+      </c>
+      <c r="D4" t="n">
+        <v>80</v>
+      </c>
+      <c r="E4" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Latha</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D5" t="n">
+        <v>67</v>
+      </c>
+      <c r="E5" t="n">
+        <v>81</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nani</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>99</v>
+      </c>
+      <c r="D6" t="n">
+        <v>74</v>
+      </c>
+      <c r="E6" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>116</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Surya</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>86</v>
+      </c>
+      <c r="D7" t="n">
+        <v>69</v>
+      </c>
+      <c r="E7" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sita</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>96</v>
+      </c>
+      <c r="D8" t="n">
         <v>65</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>gayee0131@gmail.com</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="E8" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pavi</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>88</v>
+      </c>
+      <c r="D9" t="n">
+        <v>77</v>
+      </c>
+      <c r="E9" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ajay</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>95</v>
+      </c>
+      <c r="D10" t="n">
+        <v>82</v>
+      </c>
+      <c r="E10" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sita</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>81</v>
+      </c>
+      <c r="D11" t="n">
+        <v>81</v>
+      </c>
+      <c r="E11" t="n">
+        <v>81</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mahi</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>99</v>
+      </c>
+      <c r="D12" t="n">
+        <v>94</v>
+      </c>
+      <c r="E12" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>140</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deepa</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>97</v>
+      </c>
+      <c r="D13" t="n">
+        <v>76</v>
+      </c>
+      <c r="E13" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>143</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gopi</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>82</v>
+      </c>
+      <c r="D14" t="n">
+        <v>98</v>
+      </c>
+      <c r="E14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>144</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Riya</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>85</v>
+      </c>
+      <c r="D15" t="n">
+        <v>60</v>
+      </c>
+      <c r="E15" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>145</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Asha</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>90</v>
+      </c>
+      <c r="D16" t="n">
+        <v>93</v>
+      </c>
+      <c r="E16" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Keep up the good work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>150</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Divya</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>91</v>
+      </c>
+      <c r="D17" t="n">
+        <v>89</v>
+      </c>
+      <c r="E17" t="n">
+        <v>90</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Good Performance</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Keep up the good work.</t>
         </is>

--- a/reports/safe_students.xlsx
+++ b/reports/safe_students.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,20 +439,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>PERFORMANCE SCORE</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>REASON</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SUGGESTION</t>
         </is>
@@ -460,33 +465,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Harsha</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D2" t="n">
-        <v>73</v>
-      </c>
-      <c r="E2" t="n">
-        <v>80</v>
-      </c>
-      <c r="F2" t="inlineStr">
+        <v>65</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>gayee0131@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Good Performance</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Keep up the good work.</t>
         </is>
@@ -494,33 +504,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kiran</t>
+          <t>Jaya</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
-      </c>
-      <c r="E3" t="n">
-        <v>73</v>
-      </c>
-      <c r="F3" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>gayee0131@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>85</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Good Performance</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Keep up the good work.</t>
         </is>
@@ -532,471 +547,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ram</t>
+          <t>Karthik</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
-      </c>
-      <c r="E4" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="F4" t="inlineStr">
+        <v>70</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>gayee0131@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Good Performance</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Keep up the good work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>107</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Latha</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>95</v>
-      </c>
-      <c r="D5" t="n">
-        <v>67</v>
-      </c>
-      <c r="E5" t="n">
-        <v>81</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Keep up the good work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>108</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Nani</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>99</v>
-      </c>
-      <c r="D6" t="n">
-        <v>74</v>
-      </c>
-      <c r="E6" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Keep up the good work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>116</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Surya</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>86</v>
-      </c>
-      <c r="D7" t="n">
-        <v>69</v>
-      </c>
-      <c r="E7" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Keep up the good work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>120</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Sita</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>96</v>
-      </c>
-      <c r="D8" t="n">
-        <v>65</v>
-      </c>
-      <c r="E8" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Keep up the good work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>122</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Pavi</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>88</v>
-      </c>
-      <c r="D9" t="n">
-        <v>77</v>
-      </c>
-      <c r="E9" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Keep up the good work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>130</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ajay</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>95</v>
-      </c>
-      <c r="D10" t="n">
-        <v>82</v>
-      </c>
-      <c r="E10" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Keep up the good work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>131</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Sita</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>81</v>
-      </c>
-      <c r="D11" t="n">
-        <v>81</v>
-      </c>
-      <c r="E11" t="n">
-        <v>81</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Keep up the good work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>134</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Mahi</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>99</v>
-      </c>
-      <c r="D12" t="n">
-        <v>94</v>
-      </c>
-      <c r="E12" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Keep up the good work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>140</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Deepa</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>97</v>
-      </c>
-      <c r="D13" t="n">
-        <v>76</v>
-      </c>
-      <c r="E13" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Keep up the good work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>143</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Gopi</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>82</v>
-      </c>
-      <c r="D14" t="n">
-        <v>98</v>
-      </c>
-      <c r="E14" t="n">
-        <v>90</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Keep up the good work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>144</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Riya</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>85</v>
-      </c>
-      <c r="D15" t="n">
-        <v>60</v>
-      </c>
-      <c r="E15" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Keep up the good work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>145</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Asha</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>90</v>
-      </c>
-      <c r="D16" t="n">
-        <v>93</v>
-      </c>
-      <c r="E16" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Keep up the good work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>150</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Divya</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>91</v>
-      </c>
-      <c r="D17" t="n">
-        <v>89</v>
-      </c>
-      <c r="E17" t="n">
-        <v>90</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Good Performance</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Keep up the good work.</t>
         </is>
